--- a/data-template/TES_VOCA_Lv0.xlsx
+++ b/data-template/TES_VOCA_Lv0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82107\Downloads\TES_VOCA_Lv 1,2,4,5,6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82107\Downloads\TES_APP\data-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DAB2506-DF76-4C9F-B4D7-8610AB5F0412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893EA339-5E24-454E-AC46-0D932395F5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="25" activeTab="29" xr2:uid="{873B2972-DDD5-44A0-871B-028CB8ABBB05}"/>
+    <workbookView xWindow="1700" yWindow="3390" windowWidth="19200" windowHeight="11190" firstSheet="33" activeTab="39" xr2:uid="{873B2972-DDD5-44A0-871B-028CB8ABBB05}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,16 @@
     <sheet name="Sheet28" sheetId="28" r:id="rId28"/>
     <sheet name="Sheet29" sheetId="29" r:id="rId29"/>
     <sheet name="Sheet30" sheetId="30" r:id="rId30"/>
+    <sheet name="Sheet31" sheetId="31" r:id="rId31"/>
+    <sheet name="Sheet32" sheetId="32" r:id="rId32"/>
+    <sheet name="Sheet33" sheetId="33" r:id="rId33"/>
+    <sheet name="Sheet34" sheetId="34" r:id="rId34"/>
+    <sheet name="Sheet35" sheetId="35" r:id="rId35"/>
+    <sheet name="Sheet36" sheetId="36" r:id="rId36"/>
+    <sheet name="Sheet37" sheetId="37" r:id="rId37"/>
+    <sheet name="Sheet38" sheetId="38" r:id="rId38"/>
+    <sheet name="Sheet39" sheetId="39" r:id="rId39"/>
+    <sheet name="Sheet40" sheetId="40" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="947">
   <si>
     <t>bear</t>
   </si>
@@ -2192,13 +2202,728 @@
   </si>
   <si>
     <t>The closet is big.</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>shark</t>
+  </si>
+  <si>
+    <t>sell</t>
+  </si>
+  <si>
+    <t>spider</t>
+  </si>
+  <si>
+    <t>picture</t>
+  </si>
+  <si>
+    <t>drum</t>
+  </si>
+  <si>
+    <t>corn</t>
+  </si>
+  <si>
+    <t>wet</t>
+  </si>
+  <si>
+    <t>상어</t>
+  </si>
+  <si>
+    <t>(돈을 받고) 팔다</t>
+  </si>
+  <si>
+    <t>거미</t>
+  </si>
+  <si>
+    <t>그림, 사진</t>
+  </si>
+  <si>
+    <t>북, 드럼</t>
+  </si>
+  <si>
+    <t>옥수수</t>
+  </si>
+  <si>
+    <t>젖은</t>
+  </si>
+  <si>
+    <t>movie</t>
+  </si>
+  <si>
+    <t>bubble</t>
+  </si>
+  <si>
+    <t>soft</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>listen</t>
+  </si>
+  <si>
+    <t>baseball</t>
+  </si>
+  <si>
+    <t>rock</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>영화</t>
+  </si>
+  <si>
+    <t>거품</t>
+  </si>
+  <si>
+    <t>부드러운, 푹신한</t>
+  </si>
+  <si>
+    <t>냄비</t>
+  </si>
+  <si>
+    <t>듣다</t>
+  </si>
+  <si>
+    <t>야구</t>
+  </si>
+  <si>
+    <t>바위</t>
+  </si>
+  <si>
+    <t>위로</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>rabbit</t>
+  </si>
+  <si>
+    <t>put</t>
+  </si>
+  <si>
+    <t>messy</t>
+  </si>
+  <si>
+    <t>bat</t>
+  </si>
+  <si>
+    <t>doctor</t>
+  </si>
+  <si>
+    <t>street</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>열려 있는, 열다</t>
+  </si>
+  <si>
+    <t>토끼</t>
+  </si>
+  <si>
+    <t>(장소에) 놓다</t>
+  </si>
+  <si>
+    <t>지저분한</t>
+  </si>
+  <si>
+    <t>배트, 방망이</t>
+  </si>
+  <si>
+    <t>의사</t>
+  </si>
+  <si>
+    <t>거리</t>
+  </si>
+  <si>
+    <t>왼쪽의, 왼쪽</t>
+  </si>
+  <si>
+    <t>toe</t>
+  </si>
+  <si>
+    <t>way</t>
+  </si>
+  <si>
+    <t>bathroom</t>
+  </si>
+  <si>
+    <t>share</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>hide</t>
+  </si>
+  <si>
+    <t>game</t>
+  </si>
+  <si>
+    <t>발가락</t>
+  </si>
+  <si>
+    <t>길, 방법</t>
+  </si>
+  <si>
+    <t>욕실, 화장실</t>
+  </si>
+  <si>
+    <t>나누다, 함께 쓰다</t>
+  </si>
+  <si>
+    <t>종이</t>
+  </si>
+  <si>
+    <t>오른쪽의, 오른쪽</t>
+  </si>
+  <si>
+    <t>감추다, 숨다</t>
+  </si>
+  <si>
+    <t>게임</t>
+  </si>
+  <si>
+    <t>snake</t>
+  </si>
+  <si>
+    <t>heart</t>
+  </si>
+  <si>
+    <t>wink</t>
+  </si>
+  <si>
+    <t>violin</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>soup</t>
+  </si>
+  <si>
+    <t>poor</t>
+  </si>
+  <si>
+    <t>push</t>
+  </si>
+  <si>
+    <t>뱀</t>
+  </si>
+  <si>
+    <t>심장, 마음</t>
+  </si>
+  <si>
+    <t>윙크, 윙크하다</t>
+  </si>
+  <si>
+    <t>바이올린</t>
+  </si>
+  <si>
+    <t>움직이다</t>
+  </si>
+  <si>
+    <t>수프</t>
+  </si>
+  <si>
+    <t>가난한, 불쌍한</t>
+  </si>
+  <si>
+    <t>밀다</t>
+  </si>
+  <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>brush</t>
+  </si>
+  <si>
+    <t>grapes</t>
+  </si>
+  <si>
+    <t>sunny</t>
+  </si>
+  <si>
+    <t>children</t>
+  </si>
+  <si>
+    <t>drive</t>
+  </si>
+  <si>
+    <t>eraser</t>
+  </si>
+  <si>
+    <t>벽</t>
+  </si>
+  <si>
+    <t>돈</t>
+  </si>
+  <si>
+    <t>붓</t>
+  </si>
+  <si>
+    <t>포도</t>
+  </si>
+  <si>
+    <t>화창한</t>
+  </si>
+  <si>
+    <t>어린이들</t>
+  </si>
+  <si>
+    <t>운전하다</t>
+  </si>
+  <si>
+    <t>지우개</t>
+  </si>
+  <si>
+    <t>windy</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>sick</t>
+  </si>
+  <si>
+    <t>ice cream</t>
+  </si>
+  <si>
+    <t>store</t>
+  </si>
+  <si>
+    <t>paint</t>
+  </si>
+  <si>
+    <t>basketball</t>
+  </si>
+  <si>
+    <t>sweet</t>
+  </si>
+  <si>
+    <t>바람이 부는</t>
+  </si>
+  <si>
+    <t>파란, 파란색</t>
+  </si>
+  <si>
+    <t>아픈</t>
+  </si>
+  <si>
+    <t>아이스크림</t>
+  </si>
+  <si>
+    <t>가게, 상점</t>
+  </si>
+  <si>
+    <t>(그림 물감으로) 그리다</t>
+  </si>
+  <si>
+    <t>농구</t>
+  </si>
+  <si>
+    <t>달콤한</t>
+  </si>
+  <si>
+    <t>birthday</t>
+  </si>
+  <si>
+    <t>owl</t>
+  </si>
+  <si>
+    <t>piano</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>hear</t>
+  </si>
+  <si>
+    <t>bench</t>
+  </si>
+  <si>
+    <t>clean</t>
+  </si>
+  <si>
+    <t>comb</t>
+  </si>
+  <si>
+    <t>생일</t>
+  </si>
+  <si>
+    <t>올빼미</t>
+  </si>
+  <si>
+    <t>피아노</t>
+  </si>
+  <si>
+    <t>음악</t>
+  </si>
+  <si>
+    <t>(소리를) 듣다</t>
+  </si>
+  <si>
+    <t>벤치</t>
+  </si>
+  <si>
+    <t>깨끗한, 청소하다</t>
+  </si>
+  <si>
+    <t>빗, 빗질하다</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>grow</t>
+  </si>
+  <si>
+    <t>heavy</t>
+  </si>
+  <si>
+    <t>coat</t>
+  </si>
+  <si>
+    <t>cool</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>basket</t>
+  </si>
+  <si>
+    <t>창문</t>
+  </si>
+  <si>
+    <t>자라다, 기르다</t>
+  </si>
+  <si>
+    <t>무거운</t>
+  </si>
+  <si>
+    <t>외투</t>
+  </si>
+  <si>
+    <t>시원한, 식히다</t>
+  </si>
+  <si>
+    <t>쌀, 밥</t>
+  </si>
+  <si>
+    <t>감자</t>
+  </si>
+  <si>
+    <t>바구니</t>
+  </si>
+  <si>
+    <t>pie</t>
+  </si>
+  <si>
+    <t>sky</t>
+  </si>
+  <si>
+    <t>pick</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>xylophone</t>
+  </si>
+  <si>
+    <t>nurse</t>
+  </si>
+  <si>
+    <t>dirty</t>
+  </si>
+  <si>
+    <t>stand</t>
+  </si>
+  <si>
+    <t>파이</t>
+  </si>
+  <si>
+    <t>하늘</t>
+  </si>
+  <si>
+    <t>(과일 등을) 따다, 고르다</t>
+  </si>
+  <si>
+    <t>따뜻한</t>
+  </si>
+  <si>
+    <t>실로폰</t>
+  </si>
+  <si>
+    <t>간호사</t>
+  </si>
+  <si>
+    <t>더러운</t>
+  </si>
+  <si>
+    <t>서다</t>
+  </si>
+  <si>
+    <t>노란, 노란색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It is yellow.</t>
+  </si>
+  <si>
+    <t>I see a shark.</t>
+  </si>
+  <si>
+    <t>I sell apples.</t>
+  </si>
+  <si>
+    <t>I see a spider.</t>
+  </si>
+  <si>
+    <t>I draw a picture.</t>
+  </si>
+  <si>
+    <t>I have a drum.</t>
+  </si>
+  <si>
+    <t>I eat corn.</t>
+  </si>
+  <si>
+    <t>My hands are wet.</t>
+  </si>
+  <si>
+    <t>I watch a movie.</t>
+  </si>
+  <si>
+    <t>I see a bubble.</t>
+  </si>
+  <si>
+    <t>It is soft.</t>
+  </si>
+  <si>
+    <t>I have a pot.</t>
+  </si>
+  <si>
+    <t>I listen to music.</t>
+  </si>
+  <si>
+    <t>I like baseball.</t>
+  </si>
+  <si>
+    <t>This is a rock.</t>
+  </si>
+  <si>
+    <t>Look up.</t>
+  </si>
+  <si>
+    <t>Open the door.</t>
+  </si>
+  <si>
+    <t>I see a rabbit.</t>
+  </si>
+  <si>
+    <t>Put it here.</t>
+  </si>
+  <si>
+    <t>My room is messy.</t>
+  </si>
+  <si>
+    <t>I have a bat.</t>
+  </si>
+  <si>
+    <t>He is a doctor.</t>
+  </si>
+  <si>
+    <t>I walk on the street.</t>
+  </si>
+  <si>
+    <t>Look to the left.</t>
+  </si>
+  <si>
+    <t>This is my toe.</t>
+  </si>
+  <si>
+    <t>I know the way.</t>
+  </si>
+  <si>
+    <t>I go to the bathroom.</t>
+  </si>
+  <si>
+    <t>I share my toy.</t>
+  </si>
+  <si>
+    <t>I have a paper.</t>
+  </si>
+  <si>
+    <t>Look to the right.</t>
+  </si>
+  <si>
+    <t>I hide the box.</t>
+  </si>
+  <si>
+    <t>I play a game.</t>
+  </si>
+  <si>
+    <t>I see a snake.</t>
+  </si>
+  <si>
+    <t>This is a heart.</t>
+  </si>
+  <si>
+    <t>I wink at you.</t>
+  </si>
+  <si>
+    <t>I play the violin.</t>
+  </si>
+  <si>
+    <t>I move the chair.</t>
+  </si>
+  <si>
+    <t>I eat soup.</t>
+  </si>
+  <si>
+    <t>He is poor.</t>
+  </si>
+  <si>
+    <t>Push the door.</t>
+  </si>
+  <si>
+    <t>I see a wall.</t>
+  </si>
+  <si>
+    <t>I have money.</t>
+  </si>
+  <si>
+    <t>I use a brush.</t>
+  </si>
+  <si>
+    <t>I eat grapes.</t>
+  </si>
+  <si>
+    <t>It is sunny.</t>
+  </si>
+  <si>
+    <t>I see children.</t>
+  </si>
+  <si>
+    <t>I drive a car.</t>
+  </si>
+  <si>
+    <t>I have an eraser.</t>
+  </si>
+  <si>
+    <t>It is windy.</t>
+  </si>
+  <si>
+    <t>It is blue.</t>
+  </si>
+  <si>
+    <t>I am sick.</t>
+  </si>
+  <si>
+    <t>I eat ice cream.</t>
+  </si>
+  <si>
+    <t>I go to a store.</t>
+  </si>
+  <si>
+    <t>I paint a flower.</t>
+  </si>
+  <si>
+    <t>I like basketball.</t>
+  </si>
+  <si>
+    <t>It is sweet.</t>
+  </si>
+  <si>
+    <t>Today is my birthday.</t>
+  </si>
+  <si>
+    <t>I see an owl.</t>
+  </si>
+  <si>
+    <t>I play the piano.</t>
+  </si>
+  <si>
+    <t>I hear you.</t>
+  </si>
+  <si>
+    <t>I sit on a bench.</t>
+  </si>
+  <si>
+    <t>I clean my room.</t>
+  </si>
+  <si>
+    <t>I use a comb.</t>
+  </si>
+  <si>
+    <t>I see a window.</t>
+  </si>
+  <si>
+    <t>I grow a plant.</t>
+  </si>
+  <si>
+    <t>It is heavy.</t>
+  </si>
+  <si>
+    <t>I wear a coat.</t>
+  </si>
+  <si>
+    <t>It is cool.</t>
+  </si>
+  <si>
+    <t>I eat a potato.</t>
+  </si>
+  <si>
+    <t>I have a basket.</t>
+  </si>
+  <si>
+    <t>I eat pie.</t>
+  </si>
+  <si>
+    <t>Look at the sky.</t>
+  </si>
+  <si>
+    <t>I pick an apple.</t>
+  </si>
+  <si>
+    <t>It is warm.</t>
+  </si>
+  <si>
+    <t>I play the xylophone.</t>
+  </si>
+  <si>
+    <t>She is a nurse.</t>
+  </si>
+  <si>
+    <t>My hands are dirty.</t>
+  </si>
+  <si>
+    <t>Stand up.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2234,6 +2959,29 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2263,207 +3011,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2477,10 +3027,22 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2920,90 +3482,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="1" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3019,90 +3581,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="1" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="1" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="1" t="s">
         <v>260</v>
       </c>
     </row>
@@ -3118,90 +3680,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="1" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="1" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="35">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="1" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="1" t="s">
         <v>283</v>
       </c>
     </row>
@@ -3217,90 +3779,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="1" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="1" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="1" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="1" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="1" t="s">
         <v>307</v>
       </c>
     </row>
@@ -3316,90 +3878,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="1" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="1" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="1" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="1" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="1" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="1" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="1" t="s">
         <v>331</v>
       </c>
     </row>
@@ -3415,90 +3977,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="1" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="1" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="1" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="1" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="1" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="1" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="1" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="1" t="s">
         <v>355</v>
       </c>
     </row>
@@ -3514,90 +4076,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="1" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="1" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="1" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="1" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="1" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="1" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="1" t="s">
         <v>379</v>
       </c>
     </row>
@@ -3613,90 +4175,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="1" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="1" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="1" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="1" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="1" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="52.5">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="1" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="1" t="s">
         <v>271</v>
       </c>
     </row>
@@ -3712,90 +4274,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="1" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="1" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="1" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="1" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="1" t="s">
         <v>424</v>
       </c>
     </row>
@@ -3811,90 +4373,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="1" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="1" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="1" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="1" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="1" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="52.5">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="1" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="1" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="1" t="s">
         <v>448</v>
       </c>
     </row>
@@ -3910,90 +4472,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4009,90 +4571,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="1" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="1" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="1" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="1" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="1" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="1" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="1" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="1" t="s">
         <v>472</v>
       </c>
     </row>
@@ -4108,90 +4670,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="1" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="1" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="1" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="1" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="1" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="1" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="1" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="1" t="s">
         <v>495</v>
       </c>
     </row>
@@ -4207,90 +4769,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="1" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="1" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="1" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="1" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="35">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="1" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="1" t="s">
         <v>518</v>
       </c>
     </row>
@@ -4306,90 +4868,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="1" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="1" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="1" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="1" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="1" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="1" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="1" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="1" t="s">
         <v>542</v>
       </c>
     </row>
@@ -4405,90 +4967,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="1" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="1" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="1" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="1" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="1" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="1" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="1" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="1" t="s">
         <v>566</v>
       </c>
     </row>
@@ -4504,90 +5066,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="C1" s="1" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="1" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="1" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="1" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="1" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="1" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="1" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="1" t="s">
         <v>590</v>
       </c>
     </row>
@@ -4603,90 +5165,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="1" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="1" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="1" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="1" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="1" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="1" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="1" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4702,90 +5264,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="1" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="1" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="1" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="1" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="1" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="1" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="1" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="1" t="s">
         <v>637</v>
       </c>
     </row>
@@ -4801,90 +5363,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="1" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="1" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="1" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="1" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="1" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="1" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="1" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="C8" s="64" t="s">
+      <c r="C8" s="1" t="s">
         <v>661</v>
       </c>
     </row>
@@ -4900,90 +5462,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="1" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="1" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="1" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="1" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="1" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="1" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="1" t="s">
         <v>684</v>
       </c>
     </row>
@@ -4999,90 +5561,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>71</v>
       </c>
     </row>
@@ -5098,91 +5660,987 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="1" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="1" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="1" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="1" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="1" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="1" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="1" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="1" t="s">
         <v>708</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B815FF1-2896-4AAC-9E80-002D1D476570}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17.5"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="7"/>
+    <col min="2" max="2" width="46.6640625" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>876</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC899D14-155D-427C-B115-19E9CE54074E}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C1" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="C2" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C3" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="C4" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="C5" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="72">
+      <c r="A6" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="C6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C7" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="C8" t="s">
+        <v>884</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327CFB55-C52F-4135-A67D-434B20665838}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="C1" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="C2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="C3" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="C4" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="C5" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="C6" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="C7" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="C8" t="s">
+        <v>892</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{827DF7BA-E74F-4E04-A345-7575F0B4FD7D}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="C1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="C2" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C3" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C5" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="C6" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="C7" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="C8" t="s">
+        <v>900</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC04B2A-9F4E-47B0-9CCC-91FF19707A32}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="C1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="C2" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C3" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="C4" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="C5" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C6" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="216">
+      <c r="A7" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="C7" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="C8" t="s">
+        <v>908</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF413C22-833E-431B-9B26-849D984D620E}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="C1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="C2" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="C3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="C4" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>792</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="C5" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="C6" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="C7" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="C8" t="s">
+        <v>916</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62944E06-4B73-46FA-8A7F-3A6BAE2A2591}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="C2" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>806</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="C3" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C4" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>808</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="C5" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="C6" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="72">
+      <c r="A7" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="C7" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>811</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="C8" t="s">
+        <v>924</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B38F427-D79C-4C64-918B-7255C8FBB5F7}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C1" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C2" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="C3" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="C4" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="C5" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="C6" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>834</v>
+      </c>
+      <c r="C7" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="C8" t="s">
+        <v>931</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45F9BAA-5BFD-4F5C-8C95-AB8184580BDA}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="C1" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="C2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C3" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C4" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>848</v>
+      </c>
+      <c r="C5" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="72">
+      <c r="A6" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="C6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="C7" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="C8" t="s">
+        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -5197,91 +6655,190 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="1" t="s">
         <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BF7EAC-9C79-4B52-8ED8-C06AD1AE3221}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="36">
+      <c r="A1" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C1" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="36">
+      <c r="A2" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="C2" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
+      <c r="A3" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="C3" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="C4" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="C5" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="C6" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="C7" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="C8" t="s">
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -5296,90 +6853,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="52.5">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5395,90 +6952,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="1" t="s">
         <v>142</v>
       </c>
     </row>
@@ -5494,90 +7051,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5593,90 +7150,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="1" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="1" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5692,90 +7249,90 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17.5">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.5">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.5">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.5">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="1" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.5">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.5">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="1" t="s">
         <v>213</v>
       </c>
     </row>
